--- a/NECP Scenario/Results/Regional Results/EL30_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL30_Capacity.xlsx
@@ -507,25 +507,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.176540220137452E-11</v>
+        <v>1.737117148378926E-11</v>
       </c>
       <c r="C2">
-        <v>6.16091293606787E-12</v>
+        <v>9.096368752595008E-12</v>
       </c>
       <c r="D2">
-        <v>9.052359863118875E-12</v>
+        <v>1.336547843821015E-11</v>
       </c>
       <c r="E2">
-        <v>1.330099099032205E-11</v>
+        <v>1.963841036296558E-11</v>
       </c>
       <c r="F2">
-        <v>1.95435936948092E-11</v>
+        <v>2.885535757438914E-11</v>
       </c>
       <c r="G2">
-        <v>2.871589079363148E-11</v>
+        <v>4.239789528176488E-11</v>
       </c>
       <c r="H2">
-        <v>1.740403161392616E-10</v>
+        <v>2.569638633190408E-10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.224442406857246E-08</v>
+        <v>5.721393958404547E-08</v>
       </c>
       <c r="C3">
-        <v>3.239161678302232E-08</v>
+        <v>6.467705771008135E-08</v>
       </c>
       <c r="D3">
-        <v>6.441825537335926E-08</v>
+        <v>1.215541493157124E-07</v>
       </c>
       <c r="E3">
-        <v>0.1949068386680118</v>
+        <v>0.09752567178475539</v>
       </c>
       <c r="F3">
-        <v>0.1949068064381334</v>
+        <v>0.0975256073494387</v>
       </c>
       <c r="G3">
-        <v>0.1949067748761779</v>
+        <v>0.0975255526933987</v>
       </c>
       <c r="H3">
-        <v>0.1322468466835358</v>
+        <v>0.2008461689245304</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -562,22 +562,22 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>2.388534695315899E-13</v>
+        <v>1.779795422048717E-13</v>
       </c>
       <c r="D4">
-        <v>2.396058331459207E-13</v>
+        <v>1.785058201107207E-13</v>
       </c>
       <c r="E4">
-        <v>2.404699347879169E-13</v>
+        <v>1.79108616855796E-13</v>
       </c>
       <c r="F4">
-        <v>2.412964068083428E-13</v>
+        <v>1.797020406717799E-13</v>
       </c>
       <c r="G4">
-        <v>2.422178904814666E-13</v>
+        <v>1.803743241908269E-13</v>
       </c>
       <c r="H4">
-        <v>2.436103667077963E-13</v>
+        <v>1.814009564668172E-13</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -692,22 +692,22 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>2.044586459583743E-08</v>
+        <v>4.227082550962156E-08</v>
       </c>
       <c r="D9">
-        <v>2.058938701679452E-08</v>
+        <v>4.234779437233728E-08</v>
       </c>
       <c r="E9">
-        <v>2.940716511116413E-08</v>
+        <v>4.265843703259882E-08</v>
       </c>
       <c r="F9">
-        <v>2.941839017506315E-08</v>
+        <v>4.267508612356235E-08</v>
       </c>
       <c r="G9">
-        <v>2.943647930907986E-08</v>
+        <v>4.270156605008672E-08</v>
       </c>
       <c r="H9">
-        <v>1.086236911224423E-07</v>
+        <v>1.614286455781172E-07</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -715,25 +715,25 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.9278600000035402</v>
+        <v>0.9278600000038777</v>
       </c>
       <c r="C10">
-        <v>0.927860000005115</v>
+        <v>0.9278600000059487</v>
       </c>
       <c r="D10">
-        <v>0.9278600000075018</v>
+        <v>0.9278600000092612</v>
       </c>
       <c r="E10">
-        <v>0.3776600000135212</v>
+        <v>0.377660000016142</v>
       </c>
       <c r="F10">
-        <v>1.781223136053063E-08</v>
+        <v>2.625261084608668E-08</v>
       </c>
       <c r="G10">
-        <v>1.824250498098053E-08</v>
+        <v>2.71425233100994E-08</v>
       </c>
       <c r="H10">
-        <v>1.098621391839266E-07</v>
+        <v>1.632147911899701E-07</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>8.683828912002667</v>
+        <v>8.683828912004151</v>
       </c>
       <c r="C13">
-        <v>8.683828912004389</v>
+        <v>8.683828912006685</v>
       </c>
       <c r="D13">
-        <v>8.683828912010105</v>
+        <v>8.68382891201154</v>
       </c>
       <c r="E13">
-        <v>8.683828912015347</v>
+        <v>8.683828912022168</v>
       </c>
       <c r="F13">
-        <v>8.683828912025737</v>
+        <v>8.683828912036024</v>
       </c>
       <c r="G13">
-        <v>8.683828912051688</v>
+        <v>8.683828912068927</v>
       </c>
       <c r="H13">
-        <v>8.683828912276732</v>
+        <v>8.683828912349073</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -923,25 +923,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>2.204834276191904E-08</v>
+        <v>4.10773030852657E-08</v>
       </c>
       <c r="C18">
-        <v>2.206005770293501E-08</v>
+        <v>4.109909732737349E-08</v>
       </c>
       <c r="D18">
-        <v>3.974947953386164E-08</v>
+        <v>7.86883488157779E-08</v>
       </c>
       <c r="E18">
-        <v>0.0428578409291772</v>
+        <v>0.0148182567263984</v>
       </c>
       <c r="F18">
-        <v>0.0428578410021424</v>
+        <v>0.0148182569101431</v>
       </c>
       <c r="G18">
-        <v>0.0428578411013425</v>
+        <v>0.0148182570920389</v>
       </c>
       <c r="H18">
-        <v>0.0428578423979838</v>
+        <v>0.0148182595157926</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1027,25 +1027,25 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.469112582684594E-08</v>
+        <v>3.729266874627675E-08</v>
       </c>
       <c r="C22">
-        <v>2.471963880828398E-08</v>
+        <v>3.733573437068032E-08</v>
       </c>
       <c r="D22">
-        <v>2.735425251543863E-08</v>
+        <v>4.116713386589251E-08</v>
       </c>
       <c r="E22">
-        <v>4.317203419859707E-08</v>
+        <v>6.340160666732069E-08</v>
       </c>
       <c r="F22">
-        <v>5.804463037724968E-08</v>
+        <v>8.58031859700832E-08</v>
       </c>
       <c r="G22">
-        <v>8.244700353234036E-08</v>
+        <v>1.216347105877343E-07</v>
       </c>
       <c r="H22">
-        <v>4.986172029110169E-07</v>
+        <v>7.375712209343602E-07</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>6.112559773448078E-09</v>
+        <v>8.085563265864447E-09</v>
       </c>
       <c r="D24">
-        <v>2.564456626921E-08</v>
+        <v>2.934140904505639E-08</v>
       </c>
       <c r="E24">
-        <v>4.402375761450066E-08</v>
+        <v>5.64671458179621E-08</v>
       </c>
       <c r="F24">
-        <v>8.423637074265695E-07</v>
+        <v>3.727250809123429E-07</v>
       </c>
       <c r="G24">
-        <v>0.3426056825934196</v>
+        <v>0.2339562961928275</v>
       </c>
       <c r="H24">
-        <v>1.189127582089003</v>
+        <v>0.8713705803366938</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1160,22 +1160,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>3.845203210861835E-08</v>
+        <v>4.16909238377252E-08</v>
       </c>
       <c r="D27">
-        <v>0.0206374293098859</v>
+        <v>7.838729548568053E-07</v>
       </c>
       <c r="E27">
-        <v>0.0806347107130527</v>
+        <v>0.0101305195687103</v>
       </c>
       <c r="F27">
-        <v>0.3162608005398424</v>
+        <v>0.2811173077095953</v>
       </c>
       <c r="G27">
-        <v>0.6164589030225931</v>
+        <v>0.6164588942121104</v>
       </c>
       <c r="H27">
-        <v>0.6164589037151305</v>
+        <v>0.6164589032601419</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1212,22 +1212,22 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>7.655849326203106E-09</v>
+        <v>1.230558888738415E-08</v>
       </c>
       <c r="D29">
-        <v>2.347518552613181E-08</v>
+        <v>4.211144629985928E-08</v>
       </c>
       <c r="E29">
-        <v>0.7220111206932066</v>
+        <v>1.286111875672577</v>
       </c>
       <c r="F29">
-        <v>0.7220111212871198</v>
+        <v>1.286111876486954</v>
       </c>
       <c r="G29">
-        <v>1.685581459649344</v>
+        <v>2.175513340477504</v>
       </c>
       <c r="H29">
-        <v>4.19475912831735</v>
+        <v>4.194759130563154</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1264,22 +1264,22 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>7.529318276660561E-09</v>
+        <v>1.204787929920105E-08</v>
       </c>
       <c r="D31">
-        <v>9.218814686478421E-09</v>
+        <v>1.46418623490155E-08</v>
       </c>
       <c r="E31">
-        <v>2.069250608681014E-08</v>
+        <v>2.896285570192916E-08</v>
       </c>
       <c r="F31">
-        <v>2.822113597195462E-08</v>
+        <v>4.134997394884635E-08</v>
       </c>
       <c r="G31">
-        <v>3.848739038939276E-08</v>
+        <v>5.573449692986842E-08</v>
       </c>
       <c r="H31">
-        <v>2.311055343513817E-07</v>
+        <v>3.523799073621634E-07</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1316,22 +1316,22 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>1.31981512429793E-07</v>
+        <v>6.330125697854861E-08</v>
       </c>
       <c r="D33">
-        <v>1.320447438475213E-07</v>
+        <v>7.227446172358636E-08</v>
       </c>
       <c r="E33">
-        <v>1.321172380786156E-07</v>
+        <v>8.70727859812105E-08</v>
       </c>
       <c r="F33">
-        <v>3.001493545999795E-07</v>
+        <v>3.371417054215203E-07</v>
       </c>
       <c r="G33">
-        <v>3.004734791306262E-07</v>
+        <v>3.384996441604253E-07</v>
       </c>
       <c r="H33">
-        <v>7.840811653357449E-07</v>
+        <v>1.159716896073503E-06</v>
       </c>
     </row>
     <row r="34" spans="1:8">
